--- a/sources/king_step7.xlsx
+++ b/sources/king_step7.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA184"/>
+  <dimension ref="A1:AB184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="104" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>95be151a-0e2e-48d2-8d86-e618de08433e</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>c0df4ff6-6d1d-49f6-837a-f6df5c935fd4</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>26750d14-6775-4a7e-8c08-ff3c0002c794</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>b862e55d-32bd-4896-9807-8c14dbb0b8e4</t>
         </is>
@@ -783,12 +789,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>2750c91b-08bd-4bb0-a953-91450abc6fc7</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>32cf48c0-2895-4585-b335-a87f7ed98b4d</t>
         </is>
@@ -850,12 +856,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>4d635a04-3cb3-42ca-a950-29a5ad9e4307</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>48f5ccef-336f-481f-9fce-f5b59e39c369</t>
         </is>
@@ -922,12 +928,12 @@
           <t>Can be Tech Rolled to reduce damage by half.</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>68fc0fa7-1fc5-484d-8246-e802612c3e83</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>a4310753-ae80-402c-8711-bd89673d85c3</t>
         </is>
@@ -994,12 +1000,12 @@
           <t>Use 3+4 to escape after the initial grab.</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>1c8bef18-ab7d-446c-801a-c9c8c98fccc9</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>bfc4db71-b38a-4994-9efa-8a761f4c240d</t>
         </is>
@@ -1061,12 +1067,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>33aea718-9fb6-4250-b77c-5c636edd5d9c</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>bd1e469a-7bc6-49bd-ba9c-dd951e59eaf9</t>
         </is>
@@ -1128,12 +1134,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>76e853d1-7578-41e7-90f4-8aeaa96c74d2</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>e7e1c8a7-274b-46e9-bfe3-79864f13699b</t>
         </is>
@@ -1142,22 +1148,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>b+1+2 [~5]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>b+1+2 [~5]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Irish Whip [Tag]</t>
+          <t>Irish Whip</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Irish Whip [Tag]</t>
+          <t>Irish Whip</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1202,10 +1208,15 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>538b0098-9d86-4567-b516-9349cc00921f</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>8c1b4c39-95dd-4fca-9ff1-3d1011d561bc</t>
         </is>
@@ -1214,22 +1225,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>df+3+4 [~5]</t>
+          <t>df+3+4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>df+3+4 [~5]</t>
+          <t>df+3+4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Frankensteiner [Tag]</t>
+          <t>Frankensteiner</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Frankensteiner [Tag]</t>
+          <t>Frankensteiner</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1274,10 +1285,15 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>a3aea0d4-aaf1-41ff-af11-48aab15b2b37</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>9e545cc8-68f6-4665-814a-d3cc55ce31ea</t>
         </is>
@@ -1344,12 +1360,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>dfa2bd63-632f-4f72-a736-a3a21c661f4e</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>2e57dbc5-d2ed-42ee-b13a-704d711846d4</t>
         </is>
@@ -1363,7 +1379,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>b+1+2 [~5],1+3</t>
+          <t>b+1+2,1+3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1373,7 +1389,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Irish Whip [Tag] – Feint</t>
+          <t>Irish Whip – Feint</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1401,17 +1417,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>8c1b4c39-95dd-4fca-9ff1-3d1011d561bc</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1425,7 +1441,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>b+1+2 [~5],3+4</t>
+          <t>b+1+2,3+4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1435,7 +1451,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Irish Whip [Tag] – Ground Smash</t>
+          <t>Irish Whip – Ground Smash</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1463,17 +1479,17 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>8c1b4c39-95dd-4fca-9ff1-3d1011d561bc</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1487,7 +1503,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>b+1+2 [~5],2+4</t>
+          <t>b+1+2,2+4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1497,7 +1513,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Irish Whip [Tag] – Quick Slam</t>
+          <t>Irish Whip – Quick Slam</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1525,17 +1541,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>8c1b4c39-95dd-4fca-9ff1-3d1011d561bc</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1549,7 +1565,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>b+1+2 [~5],1+2</t>
+          <t>b+1+2,1+2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1559,7 +1575,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Irish Whip [Tag] – Turn Around Feint</t>
+          <t>Irish Whip – Turn Around Feint</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1587,17 +1603,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>8c1b4c39-95dd-4fca-9ff1-3d1011d561bc</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1654,12 +1670,12 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1706,17 +1722,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1763,17 +1779,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1820,17 +1836,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1877,17 +1893,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1934,17 +1950,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1991,17 +2007,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2048,17 +2064,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2105,17 +2121,17 @@
           <t>System</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>377bd68e-1783-43e2-8c72-05143260300a</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2162,17 +2178,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>377bd68e-1783-43e2-8c72-05143260300a</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2229,12 +2245,12 @@
           <t>The Counter Hit Stomach Smash is NOT a throw but is required before you can do the 2 throw follow ups.</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2281,17 +2297,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2338,17 +2354,17 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2405,12 +2421,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2467,12 +2483,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2529,12 +2545,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2586,12 +2602,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2643,12 +2659,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>a7a77dd9-2c48-4420-8555-24aab9d0520c</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2780,20 +2796,25 @@
       </c>
       <c r="X38" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y38" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y38" s="1" t="inlineStr">
+      <c r="Z38" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z38" s="1" t="inlineStr">
+      <c r="AA38" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA38" s="1" t="inlineStr">
+      <c r="AB38" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -2850,12 +2871,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2912,12 +2933,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -2969,12 +2990,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>1a628a44-4c66-4d94-b410-673005311f11</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -3026,12 +3047,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -3083,12 +3104,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>78755529-5600-440c-8380-ad656059ff13</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -3145,12 +3166,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -3207,12 +3228,12 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -3269,12 +3290,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -3331,12 +3352,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -3393,12 +3414,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>44cede5f-e666-42c2-b9ea-20ca0d73478e</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -3530,20 +3551,25 @@
       </c>
       <c r="X51" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y51" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y51" s="1" t="inlineStr">
+      <c r="Z51" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z51" s="1" t="inlineStr">
+      <c r="AA51" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA51" s="1" t="inlineStr">
+      <c r="AB51" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3625,12 +3651,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>aa0deac0-5b61-4b0c-bafa-cb313b1a9e12</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>1b2c8a65-229b-49e5-b300-9f25552638f9</t>
         </is>
@@ -3712,12 +3738,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>2897ca80-5c31-44b8-8ec7-246f2319410c</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>7112cbd4-f442-48f9-a212-b7ac2f8c0660</t>
         </is>
@@ -3799,12 +3825,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>9ce61fa8-cc53-4f70-8f48-60f8a81d1c68</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>a130bf81-0a39-4842-825a-56b7156ffee7</t>
         </is>
@@ -3886,12 +3912,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>fce8f36b-d038-4c1c-b8f9-bbd5588d6ffe</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>546fcb3b-de0d-493a-9f13-6ce3ad1d2719</t>
         </is>
@@ -3973,12 +3999,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>35b6948a-ee9a-49a0-b06e-50558ca0a048</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>c43e8dc9-b295-41c0-8630-437582c4d72c</t>
         </is>
@@ -4060,12 +4086,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>b3ef2ebe-085f-4edc-b27c-e166e4bb0d80</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>c8f13de7-65c4-4869-a6b9-a59db5ddda38</t>
         </is>
@@ -4147,12 +4173,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>1e3db536-9ed7-4e88-b667-15f79457b3bf</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>a2aef3eb-d8fb-4543-8938-bfaa20f7f9cc</t>
         </is>
@@ -4234,12 +4260,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>8d3163af-1116-4b9a-b0c2-76648dbd3cc2</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>9cd069d2-4358-4529-83f4-1c7d1af46d89</t>
         </is>
@@ -4321,12 +4347,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>3ff3e350-20f7-47c7-b8d7-2eb8038290ce</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>39aaf789-0dc2-45f4-94f9-ec41310bbb9c</t>
         </is>
@@ -4408,12 +4434,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>f6abf488-8ef5-46ec-a39f-6cacb2ce4e38</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>3946d473-f4cc-469b-8763-1c93d535387c</t>
         </is>
@@ -4495,12 +4521,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>9c6c7716-71f8-453c-9099-bcd2992c2814</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>567a6473-8982-4cf6-8e85-5656bbd717b3</t>
         </is>
@@ -4582,12 +4608,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>5e705833-4af4-4647-8e6a-e49b8c069855</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>8a76c4bf-6197-4275-9bbc-56fbf14a1947</t>
         </is>
@@ -4669,12 +4695,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>ded43ca9-d150-4ac6-9c65-e6cd77f000a8</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>5a844aa4-9efa-4130-9de3-b9c37c7b4508</t>
         </is>
@@ -4756,12 +4782,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>5eb85065-7b98-4dd1-ac6e-c2ef614a74d3</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>59f1530b-3fa2-4486-b715-e54a6dc9c056</t>
         </is>
@@ -4843,12 +4869,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>c4ad7d4d-88fc-42f8-88e2-a42b2983966c</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>6ec01a92-33f3-4b58-86cd-404df18f907e</t>
         </is>
@@ -4930,12 +4956,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>ae0ab1d6-04ed-4ebb-af80-8e7b8bd8da00</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>d1b398df-eb28-46dd-9b19-9b2c408dde07</t>
         </is>
@@ -5017,12 +5043,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>dffc1854-926b-4539-8fca-a891f4b83113</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>ab6f43ba-dafa-47df-9c48-c0417b1f55d8</t>
         </is>
@@ -5104,12 +5130,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>de48d12d-5cbc-4ea8-a85d-19cfb381813b</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>2bdb167c-5b0b-46c1-a6c8-aa18b8838746</t>
         </is>
@@ -5191,12 +5217,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>706cb4b3-73c8-4124-a2a5-7850165c2a0f</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>f847e5fb-b8a9-46df-9827-915c84720524</t>
         </is>
@@ -5278,12 +5304,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>55f856fc-7044-47d5-8caf-2e8695934bd9</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>1d592b0e-6bd7-4649-a241-d90f5865dfca</t>
         </is>
@@ -5365,12 +5391,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>2bca5625-3970-47f0-94b5-ad43a74528e3</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>06ee22cf-b7a8-4287-ad5a-c5401f72ce53</t>
         </is>
@@ -5452,12 +5478,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>1fde0215-55be-41dd-8a09-f0040943e3c2</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>af0703e1-7625-4ef6-9eae-581f8e0ad580</t>
         </is>
@@ -5539,12 +5565,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>7ebcd40f-558a-4463-900f-4089c08d5ff7</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>01c5031e-064a-4c63-a873-e9f4dd3b3280</t>
         </is>
@@ -5626,12 +5652,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>dfea2125-4aa0-485c-bc3d-c03b02f454e5</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>9cab85f5-3446-4b67-b57d-4a6951a9db96</t>
         </is>
@@ -5763,20 +5789,25 @@
       </c>
       <c r="X78" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y78" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y78" s="1" t="inlineStr">
+      <c r="Z78" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z78" s="1" t="inlineStr">
+      <c r="AA78" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA78" s="1" t="inlineStr">
+      <c r="AB78" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -5828,12 +5859,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>b138655a-93c7-48b6-9c9d-1c66e6be9bc9</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>e7049de2-2c39-448c-839e-f9e3e6faa18c</t>
         </is>
@@ -5925,12 +5956,12 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>38072ecb-898e-46b3-93b6-fb3e4f97909e</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>667add97-85c3-4763-b63c-e961437299cb</t>
         </is>
@@ -6027,12 +6058,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>b05e4b3d-d7aa-46f3-825c-8753dbaa56bc</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>43222e74-e75d-4a17-b8a0-776bfcaa5af6</t>
         </is>
@@ -6124,12 +6155,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>95eb1f9a-a1a9-4dd3-9414-7f70101b35db</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>a8db409e-e056-44ba-9af8-4b3d9f34507d</t>
         </is>
@@ -6221,12 +6252,12 @@
           <t>sm</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>3e3dd020-b50e-4c60-8f81-cebf3bc6050e</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>7bd4d6e1-3270-43da-ac34-b5b9f7a0852e</t>
         </is>
@@ -6323,12 +6354,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>265c065f-9246-44d7-8c40-2e1e50ad0838</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>a45ab1bf-c696-4ea6-8a20-901efdd0cb75</t>
         </is>
@@ -6425,12 +6456,12 @@
           <t>BT</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>1b29a001-8eab-4ef2-aa49-73518b87fa72</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>7f59ce8c-1210-41bf-82ce-3d93444e9bb1</t>
         </is>
@@ -6517,17 +6548,17 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>0bc84b49-489e-41f1-9ff2-4cf99618d4f8</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>c92002e3-0b6b-491d-90ff-92f669f8e377</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>1b29a001-8eab-4ef2-aa49-73518b87fa72</t>
         </is>
@@ -6624,12 +6655,12 @@
           <t>BNc</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>b58377e9-ad01-4cb0-8f76-d2abc1e34b96</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>61dce6e8-a91d-41d7-8f8b-117384d3eb70</t>
         </is>
@@ -6726,12 +6757,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>294f5be0-d0ab-446c-8dfe-7c7b8d013025</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>b6cad55a-ec14-45c5-95f5-7ffb365f48f9</t>
         </is>
@@ -6823,12 +6854,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>63645a74-543d-48c0-81d1-eb9a8012481f</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>3bccbe3b-907a-474e-87a3-e15a42c7a6f5</t>
         </is>
@@ -6930,12 +6961,12 @@
           <t>Hits high at the start of the move or low at the end. It only hits once. Damage remains the same.</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>afe36d1d-445c-45c7-aada-5f2ad86ab08a</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>fcc7e15d-63cc-4a4f-809d-dd4bb05418c0</t>
         </is>
@@ -7027,12 +7058,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>7fbeff82-a90b-4d4d-8c20-6f5108977c03</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>2d7911eb-85c4-47a9-9fe9-1df77f07e059</t>
         </is>
@@ -7124,12 +7155,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>f3927ada-d948-4b09-beaf-d37df9f177b9</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>e8798d6d-7946-4ee4-9210-2b492cf303d1</t>
         </is>
@@ -7221,12 +7252,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>dd925462-581e-49c8-8a60-6285e3ffc01f</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>03d17766-bbd5-4708-a17d-5ec225a816e8</t>
         </is>
@@ -7318,12 +7349,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>faf737ee-ead9-45f8-b7ec-f61d4db381cb</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>095a1794-89e3-424e-8a8e-2803b4d84738</t>
         </is>
@@ -7332,22 +7363,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FC+df+2 [~5]</t>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FC+df+2 [~5]</t>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Dynamite Upper - [Tag]</t>
+          <t>Dynamite Upper -</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dynamite Upper - [Tag]</t>
+          <t>Dynamite Upper -</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7422,10 +7453,15 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
           <t>62190769-ac4f-416d-852c-8126eed7a0d9</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>1f287385-1f96-426c-870c-402840a004d3</t>
         </is>
@@ -7434,22 +7470,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>f,f+2 [~5]</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>f,f+2 [~5]</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>K's Flicker - [Tag]</t>
+          <t>K's Flicker -</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>K's Flicker - [Tag]</t>
+          <t>K's Flicker -</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7524,10 +7560,15 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
           <t>5e49b348-140b-42c2-86ec-5d54ab5628fe</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>72471442-53d0-431f-8236-53c40439baf9</t>
         </is>
@@ -7624,12 +7665,12 @@
           <t>DSc</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>292f9d40-4e72-4d88-b636-725d916a2c6f</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>8dd9cb5f-b8be-48a5-882f-dbf20f5f5ff4</t>
         </is>
@@ -7706,17 +7747,17 @@
           <t>Throws are only possible after a counter hit. Check the throws listing for escapes.</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>defc8ed1-a987-4805-a78e-39f6f81afdca</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>703cd568-b29b-4a22-8da0-000a08343be3</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>292f9d40-4e72-4d88-b636-725d916a2c6f</t>
         </is>
@@ -7793,17 +7834,17 @@
           <t>Throws are only possible after a counter hit. Check the throws listing for escapes.</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>7c2fa24b-55b9-4021-b99b-4d0bfba4f94b</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>96f11ea4-bcfe-4694-bfea-b644e7379f5d</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>292f9d40-4e72-4d88-b636-725d916a2c6f</t>
         </is>
@@ -7900,12 +7941,12 @@
           <t>FSc</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>341b1d54-7f22-4406-bd8d-8add0f5e8e0d</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>7549698b-4fc3-4785-9e91-f35a087d6754</t>
         </is>
@@ -8002,12 +8043,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>6d79992b-ba4b-430f-af7d-f69d678a9499</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>e39b12da-3df5-42e2-9e1b-fd8eb9de1204</t>
         </is>
@@ -8104,12 +8145,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>865dbe87-35cb-414f-99ab-8af114313aa1</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>738a8815-05e2-4eea-9bcb-3ee8398a6f5d</t>
         </is>
@@ -8201,12 +8242,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>08cf9ef0-bd63-4746-a8bb-12b265288362</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>dc6c5be5-8257-4655-b39a-7ae023ff024c</t>
         </is>
@@ -8298,12 +8339,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>ffe56755-6d81-4a5b-829b-8939fdf90ef1</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>b6a82ba7-cb30-4931-8280-fca14f392078</t>
         </is>
@@ -8400,12 +8441,12 @@
           <t>CSc MS</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="Y105" t="inlineStr">
         <is>
           <t>b8dd73d8-ecca-493d-bd42-2d30cc54230c</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>3e80ea99-a1b5-44e5-9130-fff19e637ba5</t>
         </is>
@@ -8507,12 +8548,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>89832bf8-c8bb-4a3f-9f8b-5089f80f8f12</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>de67f9ea-315f-4da6-b452-5618ec41a37a</t>
         </is>
@@ -8614,12 +8655,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
+      <c r="Y107" t="inlineStr">
         <is>
           <t>6db95b24-b422-4e45-a958-3c1559dc0f87</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>d5fce58a-08c7-4981-8075-283c4fb33e64</t>
         </is>
@@ -8716,12 +8757,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
+      <c r="Y108" t="inlineStr">
         <is>
           <t>f3cff471-aa19-4c5a-bf22-98f241b0c581</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
+      <c r="Z108" t="inlineStr">
         <is>
           <t>216ebcfa-7868-4913-a68e-fa3b828502a0</t>
         </is>
@@ -8828,12 +8869,12 @@
           <t>Damage is 13 when no second kick is buffered.</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="Y109" t="inlineStr">
         <is>
           <t>24208035-ffdd-4ae3-a9ac-2f788c6f8375</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>5e927ca4-6f91-4c7d-9591-f6bae2a08ad0</t>
         </is>
@@ -8920,17 +8961,17 @@
           <t>Lm</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="Y110" t="inlineStr">
         <is>
           <t>1e28a921-b606-46f7-bce8-b2905592318b</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>f4594c77-9235-4bef-913e-994e42adf856</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
+      <c r="AA110" t="inlineStr">
         <is>
           <t>24208035-ffdd-4ae3-a9ac-2f788c6f8375</t>
         </is>
@@ -9022,17 +9063,17 @@
           <t>The Spin Upper after 2 or 3 Ali Kicks is only possible if the 1st Ali Kick was a Counter Hit.</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
+      <c r="Y111" t="inlineStr">
         <is>
           <t>cce7caab-ca6f-4ea2-ba29-cf030e04e34e</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>aced7dcf-e48f-439c-8031-19160a1fb2aa</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
+      <c r="AA111" t="inlineStr">
         <is>
           <t>24208035-ffdd-4ae3-a9ac-2f788c6f8375</t>
         </is>
@@ -9124,17 +9165,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
+      <c r="Y112" t="inlineStr">
         <is>
           <t>3b86ae10-c611-4231-a8d2-992ddea22633</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
+      <c r="Z112" t="inlineStr">
         <is>
           <t>b7668c9c-b1f0-4095-aabe-2f3c2a3142e7</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
+      <c r="AA112" t="inlineStr">
         <is>
           <t>24208035-ffdd-4ae3-a9ac-2f788c6f8375</t>
         </is>
@@ -9226,17 +9267,17 @@
           <t>The Spin Upper after 2 or 3 Ali Kicks is only possible if the 1st Ali Kick was a Counter Hit.</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="Y113" t="inlineStr">
         <is>
           <t>96c47490-e2ba-4ce4-85bc-3c7b3c3d04b5</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
+      <c r="Z113" t="inlineStr">
         <is>
           <t>788cb04a-2fb7-498f-bf07-7f3deebc1ab1</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
+      <c r="AA113" t="inlineStr">
         <is>
           <t>3b86ae10-c611-4231-a8d2-992ddea22633</t>
         </is>
@@ -9333,17 +9374,17 @@
           <t>Extended Ali Kicks can only be done if the 1st Ali Kick was a counter hit.</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="Y114" t="inlineStr">
         <is>
           <t>4a8e08d7-31c6-4f54-8b1d-a3c1f506ca1b</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="Z114" t="inlineStr">
         <is>
           <t>1a46f7f9-c39e-4ba5-8528-88bf8273e152</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
+      <c r="AA114" t="inlineStr">
         <is>
           <t>3b86ae10-c611-4231-a8d2-992ddea22633</t>
         </is>
@@ -9400,12 +9441,12 @@
           <t>Will throw when hitting a standing opponent. Damage of the throw is 45. Only tags after a throw.</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="Y115" t="inlineStr">
         <is>
           <t>dce92f10-0f51-469d-a758-987576dd74a0</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
+      <c r="Z115" t="inlineStr">
         <is>
           <t>29efa738-0283-4cd9-9e7a-2569a95d7c0f</t>
         </is>
@@ -9497,12 +9538,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="Y116" t="inlineStr">
         <is>
           <t>52751896-a5c9-431c-9a96-0138ff488c85</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="Z116" t="inlineStr">
         <is>
           <t>afbb9de4-bf70-41f8-8d11-b0200e363416</t>
         </is>
@@ -9599,12 +9640,12 @@
           <t>BT</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="Y117" t="inlineStr">
         <is>
           <t>fcebbec8-088c-493a-b9ff-679e0167fce4</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Z117" t="inlineStr">
         <is>
           <t>ac840e59-9600-4477-8e1c-77b2a1f503f0</t>
         </is>
@@ -9696,12 +9737,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="Y118" t="inlineStr">
         <is>
           <t>9a596fc9-36be-4f1a-a729-c74324f5ca3a</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>49e20589-b379-4487-aa38-f68109cd8ea6</t>
         </is>
@@ -9793,12 +9834,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="Y119" t="inlineStr">
         <is>
           <t>76e2bc13-a52c-4ca2-8d92-2c8cbf2247ed</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>b9554727-ece1-4616-a530-bf17406394da</t>
         </is>
@@ -9855,12 +9896,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="Y120" t="inlineStr">
         <is>
           <t>1343ec62-e426-48ba-8b42-cfb43c0a4e8a</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Z120" t="inlineStr">
         <is>
           <t>76f06ebe-b5ea-4da6-a0b8-cd68bdfb2c01</t>
         </is>
@@ -9917,12 +9958,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
+      <c r="Y121" t="inlineStr">
         <is>
           <t>f50f42f7-46b7-4746-afb0-38df9e979bbf</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Z121" t="inlineStr">
         <is>
           <t>dbbfca0e-159c-4be2-87a7-8e2ef25901ac</t>
         </is>
@@ -9979,12 +10020,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="Y122" t="inlineStr">
         <is>
           <t>0161de8b-e5bc-4acc-b62c-9285ddb57ad1</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Z122" t="inlineStr">
         <is>
           <t>2bd709fb-d2f1-47b5-88fa-a91abc8ead03</t>
         </is>
@@ -10116,20 +10157,25 @@
       </c>
       <c r="X125" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y125" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y125" s="1" t="inlineStr">
+      <c r="Z125" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z125" s="1" t="inlineStr">
+      <c r="AA125" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA125" s="1" t="inlineStr">
+      <c r="AB125" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -10201,12 +10247,12 @@
           <t>50</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
+      <c r="Y126" t="inlineStr">
         <is>
           <t>6899439f-f267-4a75-b3c5-195232dd51da</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Z126" t="inlineStr">
         <is>
           <t>a56b47cf-c842-466f-af60-296937c648b3</t>
         </is>
@@ -10278,12 +10324,12 @@
           <t>50</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
+      <c r="Y127" t="inlineStr">
         <is>
           <t>35d93d75-10f1-48e5-996f-8fcff81c9409</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Z127" t="inlineStr">
         <is>
           <t>d80010c7-0746-4456-8e1c-d38f543dc57f</t>
         </is>
@@ -10375,12 +10421,12 @@
           <t>Can be done from Back Turned Position.</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
+      <c r="Y128" t="inlineStr">
         <is>
           <t>58eef5e5-4e01-4937-8c56-c2f8a10b50f9</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Z128" t="inlineStr">
         <is>
           <t>39eb2f42-6c9c-4e2d-956b-b21842a6e66e</t>
         </is>
@@ -10512,20 +10558,25 @@
       </c>
       <c r="X131" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y131" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y131" s="1" t="inlineStr">
+      <c r="Z131" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z131" s="1" t="inlineStr">
+      <c r="AA131" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA131" s="1" t="inlineStr">
+      <c r="AB131" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -10577,12 +10628,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y132" t="inlineStr">
+      <c r="Z132" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
         </is>
       </c>
-      <c r="AA132" t="inlineStr">
+      <c r="AB132" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10629,17 +10680,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
+      <c r="Z133" t="inlineStr">
         <is>
           <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
+      <c r="AA133" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
         </is>
       </c>
-      <c r="AA133" t="inlineStr">
+      <c r="AB133" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10686,17 +10737,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
+      <c r="Z134" t="inlineStr">
         <is>
           <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
+      <c r="AA134" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
         </is>
       </c>
-      <c r="AA134" t="inlineStr">
+      <c r="AB134" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10743,17 +10794,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y135" t="inlineStr">
+      <c r="Z135" t="inlineStr">
         <is>
           <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
+      <c r="AA135" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
         </is>
       </c>
-      <c r="AA135" t="inlineStr">
+      <c r="AB135" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10800,17 +10851,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr">
+      <c r="Z136" t="inlineStr">
         <is>
           <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
+      <c r="AA136" t="inlineStr">
         <is>
           <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
         </is>
       </c>
-      <c r="AA136" t="inlineStr">
+      <c r="AB136" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10867,12 +10918,12 @@
           <t>After the initial grab use 3+4 to escape.</t>
         </is>
       </c>
-      <c r="Y137" t="inlineStr">
+      <c r="Z137" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
         </is>
       </c>
-      <c r="AA137" t="inlineStr">
+      <c r="AB137" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10924,17 +10975,17 @@
           <t>Double Arm Face Buster is not additional damage to the Jaguar Driver, it add 5 points of damage.</t>
         </is>
       </c>
-      <c r="Y138" t="inlineStr">
+      <c r="Z138" t="inlineStr">
         <is>
           <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
+      <c r="AA138" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
         </is>
       </c>
-      <c r="AA138" t="inlineStr">
+      <c r="AB138" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10981,17 +11032,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y139" t="inlineStr">
+      <c r="Z139" t="inlineStr">
         <is>
           <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
+      <c r="AA139" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
         </is>
       </c>
-      <c r="AA139" t="inlineStr">
+      <c r="AB139" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11043,12 +11094,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y140" t="inlineStr">
+      <c r="Z140" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
         </is>
       </c>
-      <c r="AA140" t="inlineStr">
+      <c r="AB140" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11095,17 +11146,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y141" t="inlineStr">
+      <c r="Z141" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
+      <c r="AA141" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
         </is>
       </c>
-      <c r="AA141" t="inlineStr">
+      <c r="AB141" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11152,17 +11203,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y142" t="inlineStr">
+      <c r="Z142" t="inlineStr">
         <is>
           <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
+      <c r="AA142" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
         </is>
       </c>
-      <c r="AA142" t="inlineStr">
+      <c r="AB142" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11209,17 +11260,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y143" t="inlineStr">
+      <c r="Z143" t="inlineStr">
         <is>
           <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
+      <c r="AA143" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
         </is>
       </c>
-      <c r="AA143" t="inlineStr">
+      <c r="AB143" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11266,17 +11317,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y144" t="inlineStr">
+      <c r="Z144" t="inlineStr">
         <is>
           <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
+      <c r="AA144" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
         </is>
       </c>
-      <c r="AA144" t="inlineStr">
+      <c r="AB144" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11323,17 +11374,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y145" t="inlineStr">
+      <c r="Z145" t="inlineStr">
         <is>
           <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
+      <c r="AA145" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
         </is>
       </c>
-      <c r="AA145" t="inlineStr">
+      <c r="AB145" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11380,17 +11431,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y146" t="inlineStr">
+      <c r="Z146" t="inlineStr">
         <is>
           <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
+      <c r="AA146" t="inlineStr">
         <is>
           <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
         </is>
       </c>
-      <c r="AA146" t="inlineStr">
+      <c r="AB146" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11452,12 +11503,12 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
-      <c r="Y147" t="inlineStr">
+      <c r="Z147" t="inlineStr">
         <is>
           <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
         </is>
       </c>
-      <c r="AA147" t="inlineStr">
+      <c r="AB147" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11509,17 +11560,17 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
-      <c r="Y148" t="inlineStr">
+      <c r="Z148" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
+      <c r="AA148" t="inlineStr">
         <is>
           <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
         </is>
       </c>
-      <c r="AA148" t="inlineStr">
+      <c r="AB148" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11566,17 +11617,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
+      <c r="Z149" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
+      <c r="AA149" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
         </is>
       </c>
-      <c r="AA149" t="inlineStr">
+      <c r="AB149" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11623,17 +11674,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y150" t="inlineStr">
+      <c r="Z150" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
+      <c r="AA150" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
         </is>
       </c>
-      <c r="AA150" t="inlineStr">
+      <c r="AB150" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11680,17 +11731,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y151" t="inlineStr">
+      <c r="Z151" t="inlineStr">
         <is>
           <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
+      <c r="AA151" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
         </is>
       </c>
-      <c r="AA151" t="inlineStr">
+      <c r="AB151" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11737,17 +11788,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y152" t="inlineStr">
+      <c r="Z152" t="inlineStr">
         <is>
           <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
+      <c r="AA152" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
         </is>
       </c>
-      <c r="AA152" t="inlineStr">
+      <c r="AB152" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11794,17 +11845,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y153" t="inlineStr">
+      <c r="Z153" t="inlineStr">
         <is>
           <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
+      <c r="AA153" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
         </is>
       </c>
-      <c r="AA153" t="inlineStr">
+      <c r="AB153" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11851,17 +11902,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y154" t="inlineStr">
+      <c r="Z154" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
+      <c r="AA154" t="inlineStr">
         <is>
           <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
         </is>
       </c>
-      <c r="AA154" t="inlineStr">
+      <c r="AB154" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11908,17 +11959,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y155" t="inlineStr">
+      <c r="Z155" t="inlineStr">
         <is>
           <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
+      <c r="AA155" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
         </is>
       </c>
-      <c r="AA155" t="inlineStr">
+      <c r="AB155" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11965,17 +12016,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y156" t="inlineStr">
+      <c r="Z156" t="inlineStr">
         <is>
           <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
+      <c r="AA156" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
         </is>
       </c>
-      <c r="AA156" t="inlineStr">
+      <c r="AB156" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12022,17 +12073,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y157" t="inlineStr">
+      <c r="Z157" t="inlineStr">
         <is>
           <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
+      <c r="AA157" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
         </is>
       </c>
-      <c r="AA157" t="inlineStr">
+      <c r="AB157" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12079,17 +12130,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y158" t="inlineStr">
+      <c r="Z158" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
+      <c r="AA158" t="inlineStr">
         <is>
           <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
         </is>
       </c>
-      <c r="AA158" t="inlineStr">
+      <c r="AB158" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12136,17 +12187,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y159" t="inlineStr">
+      <c r="Z159" t="inlineStr">
         <is>
           <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
+      <c r="AA159" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
         </is>
       </c>
-      <c r="AA159" t="inlineStr">
+      <c r="AB159" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12193,17 +12244,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y160" t="inlineStr">
+      <c r="Z160" t="inlineStr">
         <is>
           <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
+      <c r="AA160" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
         </is>
       </c>
-      <c r="AA160" t="inlineStr">
+      <c r="AB160" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12255,12 +12306,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y161" t="inlineStr">
+      <c r="Z161" t="inlineStr">
         <is>
           <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
         </is>
       </c>
-      <c r="AA161" t="inlineStr">
+      <c r="AB161" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12317,12 +12368,12 @@
           <t>If grabbed from the side or back then Cannonball will be the 1st part of the Multi Throw.</t>
         </is>
       </c>
-      <c r="Y162" t="inlineStr">
+      <c r="Z162" t="inlineStr">
         <is>
           <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
         </is>
       </c>
-      <c r="AA162" t="inlineStr">
+      <c r="AB162" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12374,12 +12425,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y163" t="inlineStr">
+      <c r="Z163" t="inlineStr">
         <is>
           <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
         </is>
       </c>
-      <c r="AA163" t="inlineStr">
+      <c r="AB163" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12426,17 +12477,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y164" t="inlineStr">
+      <c r="Z164" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
+      <c r="AA164" t="inlineStr">
         <is>
           <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
         </is>
       </c>
-      <c r="AA164" t="inlineStr">
+      <c r="AB164" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12483,17 +12534,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y165" t="inlineStr">
+      <c r="Z165" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
+      <c r="AA165" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
         </is>
       </c>
-      <c r="AA165" t="inlineStr">
+      <c r="AB165" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12540,17 +12591,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y166" t="inlineStr">
+      <c r="Z166" t="inlineStr">
         <is>
           <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
+      <c r="AA166" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
         </is>
       </c>
-      <c r="AA166" t="inlineStr">
+      <c r="AB166" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12597,17 +12648,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y167" t="inlineStr">
+      <c r="Z167" t="inlineStr">
         <is>
           <t>58f13036-58ee-4611-a14d-d783777422a0</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
+      <c r="AA167" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
         </is>
       </c>
-      <c r="AA167" t="inlineStr">
+      <c r="AB167" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12654,17 +12705,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y168" t="inlineStr">
+      <c r="Z168" t="inlineStr">
         <is>
           <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
+      <c r="AA168" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
         </is>
       </c>
-      <c r="AA168" t="inlineStr">
+      <c r="AB168" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12711,17 +12762,17 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y169" t="inlineStr">
+      <c r="Z169" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
         </is>
       </c>
-      <c r="Z169" t="inlineStr">
+      <c r="AA169" t="inlineStr">
         <is>
           <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
         </is>
       </c>
-      <c r="AA169" t="inlineStr">
+      <c r="AB169" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12768,17 +12819,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y170" t="inlineStr">
+      <c r="Z170" t="inlineStr">
         <is>
           <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
+      <c r="AA170" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
         </is>
       </c>
-      <c r="AA170" t="inlineStr">
+      <c r="AB170" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12825,17 +12876,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y171" t="inlineStr">
+      <c r="Z171" t="inlineStr">
         <is>
           <t>cd229188-1f00-4e2c-beb7-0ecdab35b8dc</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
+      <c r="AA171" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
         </is>
       </c>
-      <c r="AA171" t="inlineStr">
+      <c r="AB171" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -12967,20 +13018,25 @@
       </c>
       <c r="X174" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y174" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y174" s="1" t="inlineStr">
+      <c r="Z174" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z174" s="1" t="inlineStr">
+      <c r="AA174" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA174" s="1" t="inlineStr">
+      <c r="AB174" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -13022,12 +13078,12 @@
           <t>hhmmhLLLmM</t>
         </is>
       </c>
-      <c r="Y175" t="inlineStr">
+      <c r="Z175" t="inlineStr">
         <is>
           <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
         </is>
       </c>
-      <c r="AA175" t="inlineStr">
+      <c r="AB175" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13069,12 +13125,12 @@
           <t>hhmmhLLLmh</t>
         </is>
       </c>
-      <c r="Y176" t="inlineStr">
+      <c r="Z176" t="inlineStr">
         <is>
           <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
         </is>
       </c>
-      <c r="AA176" t="inlineStr">
+      <c r="AB176" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13116,12 +13172,12 @@
           <t>hhmmhmLLmM</t>
         </is>
       </c>
-      <c r="Y177" t="inlineStr">
+      <c r="Z177" t="inlineStr">
         <is>
           <t>d76e55af-5e37-469f-b459-858d5c452608</t>
         </is>
       </c>
-      <c r="AA177" t="inlineStr">
+      <c r="AB177" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13163,12 +13219,12 @@
           <t>hhmmhmLLmh</t>
         </is>
       </c>
-      <c r="Y178" t="inlineStr">
+      <c r="Z178" t="inlineStr">
         <is>
           <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
         </is>
       </c>
-      <c r="AA178" t="inlineStr">
+      <c r="AB178" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13210,12 +13266,12 @@
           <t>hhmmhmLLlthrow</t>
         </is>
       </c>
-      <c r="Y179" t="inlineStr">
+      <c r="Z179" t="inlineStr">
         <is>
           <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
         </is>
       </c>
-      <c r="AA179" t="inlineStr">
+      <c r="AB179" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13257,12 +13313,12 @@
           <t>hmmhLLLmM</t>
         </is>
       </c>
-      <c r="Y180" t="inlineStr">
+      <c r="Z180" t="inlineStr">
         <is>
           <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
         </is>
       </c>
-      <c r="AA180" t="inlineStr">
+      <c r="AB180" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13304,12 +13360,12 @@
           <t>hmmhLLLmh</t>
         </is>
       </c>
-      <c r="Y181" t="inlineStr">
+      <c r="Z181" t="inlineStr">
         <is>
           <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
         </is>
       </c>
-      <c r="AA181" t="inlineStr">
+      <c r="AB181" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13351,12 +13407,12 @@
           <t>hmmhmLLmM</t>
         </is>
       </c>
-      <c r="Y182" t="inlineStr">
+      <c r="Z182" t="inlineStr">
         <is>
           <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
         </is>
       </c>
-      <c r="AA182" t="inlineStr">
+      <c r="AB182" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13398,12 +13454,12 @@
           <t>hmmhmLLmh</t>
         </is>
       </c>
-      <c r="Y183" t="inlineStr">
+      <c r="Z183" t="inlineStr">
         <is>
           <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
         </is>
       </c>
-      <c r="AA183" t="inlineStr">
+      <c r="AB183" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -13445,12 +13501,12 @@
           <t>hmmhmLLlthrow</t>
         </is>
       </c>
-      <c r="Y184" t="inlineStr">
+      <c r="Z184" t="inlineStr">
         <is>
           <t>9aa5afc6-6646-4750-b84c-b3114de16321</t>
         </is>
       </c>
-      <c r="AA184" t="inlineStr">
+      <c r="AB184" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/king_step7.xlsx
+++ b/sources/king_step7.xlsx
@@ -10408,12 +10408,12 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">

--- a/sources/king_step7.xlsx
+++ b/sources/king_step7.xlsx
@@ -1417,6 +1417,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1479,6 +1484,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1541,6 +1551,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>f8794d93-a444-4657-859f-d2548700e248</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1603,6 +1618,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
@@ -1670,6 +1690,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
@@ -1722,6 +1747,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
@@ -1779,6 +1809,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr">
         <is>
           <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
@@ -1836,6 +1871,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
@@ -1893,6 +1933,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr">
         <is>
           <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
@@ -1950,6 +1995,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
+        </is>
+      </c>
       <c r="Z23" t="inlineStr">
         <is>
           <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
@@ -2007,6 +2057,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
+        </is>
+      </c>
       <c r="Z24" t="inlineStr">
         <is>
           <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
@@ -2064,6 +2119,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
+        </is>
+      </c>
       <c r="Z25" t="inlineStr">
         <is>
           <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
@@ -2121,6 +2181,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>377bd68e-1783-43e2-8c72-05143260300a</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr">
         <is>
           <t>377bd68e-1783-43e2-8c72-05143260300a</t>
@@ -2178,6 +2243,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr">
         <is>
           <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
@@ -2245,6 +2315,11 @@
           <t>The Counter Hit Stomach Smash is NOT a throw but is required before you can do the 2 throw follow ups.</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
+        </is>
+      </c>
       <c r="Z28" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
@@ -2297,6 +2372,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
+        </is>
+      </c>
       <c r="Z29" t="inlineStr">
         <is>
           <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
@@ -2354,6 +2434,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
+        </is>
+      </c>
       <c r="Z30" t="inlineStr">
         <is>
           <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
@@ -2421,6 +2506,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
+        </is>
+      </c>
       <c r="Z31" t="inlineStr">
         <is>
           <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
@@ -2483,6 +2573,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
+        </is>
+      </c>
       <c r="Z32" t="inlineStr">
         <is>
           <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
@@ -2545,6 +2640,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
+        </is>
+      </c>
       <c r="Z33" t="inlineStr">
         <is>
           <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
@@ -2602,6 +2702,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
+        </is>
+      </c>
       <c r="Z34" t="inlineStr">
         <is>
           <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
@@ -2657,6 +2762,11 @@
       <c r="U35" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>a7a77dd9-2c48-4420-8555-24aab9d0520c</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -2871,6 +2981,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
+        </is>
+      </c>
       <c r="Z39" t="inlineStr">
         <is>
           <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
@@ -2933,6 +3048,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
+        </is>
+      </c>
       <c r="Z40" t="inlineStr">
         <is>
           <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
@@ -2990,6 +3110,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1a628a44-4c66-4d94-b410-673005311f11</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr">
         <is>
           <t>1a628a44-4c66-4d94-b410-673005311f11</t>
@@ -3047,6 +3172,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr">
         <is>
           <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
@@ -3104,6 +3234,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>78755529-5600-440c-8380-ad656059ff13</t>
+        </is>
+      </c>
       <c r="Z43" t="inlineStr">
         <is>
           <t>78755529-5600-440c-8380-ad656059ff13</t>
@@ -3166,6 +3301,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
+        </is>
+      </c>
       <c r="Z44" t="inlineStr">
         <is>
           <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
@@ -3228,6 +3368,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
+        </is>
+      </c>
       <c r="Z45" t="inlineStr">
         <is>
           <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
@@ -3290,6 +3435,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
+        </is>
+      </c>
       <c r="Z46" t="inlineStr">
         <is>
           <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
@@ -3352,6 +3502,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
+        </is>
+      </c>
       <c r="Z47" t="inlineStr">
         <is>
           <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
@@ -3412,6 +3567,11 @@
       <c r="U48" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>44cede5f-e666-42c2-b9ea-20ca0d73478e</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -10628,6 +10788,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
+        </is>
+      </c>
       <c r="Z132" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
@@ -10680,6 +10845,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
+        </is>
+      </c>
       <c r="Z133" t="inlineStr">
         <is>
           <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
@@ -10737,6 +10907,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
+        </is>
+      </c>
       <c r="Z134" t="inlineStr">
         <is>
           <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
@@ -10794,6 +10969,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
+        </is>
+      </c>
       <c r="Z135" t="inlineStr">
         <is>
           <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
@@ -10851,6 +11031,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
+        </is>
+      </c>
       <c r="Z136" t="inlineStr">
         <is>
           <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
@@ -10918,6 +11103,11 @@
           <t>After the initial grab use 3+4 to escape.</t>
         </is>
       </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
+        </is>
+      </c>
       <c r="Z137" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
@@ -10975,6 +11165,11 @@
           <t>Double Arm Face Buster is not additional damage to the Jaguar Driver, it add 5 points of damage.</t>
         </is>
       </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
+        </is>
+      </c>
       <c r="Z138" t="inlineStr">
         <is>
           <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
@@ -11032,6 +11227,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
+        </is>
+      </c>
       <c r="Z139" t="inlineStr">
         <is>
           <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
@@ -11094,6 +11294,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>d0dc416c-d281-41de-a830-391175b9c733</t>
+        </is>
+      </c>
       <c r="Z140" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
@@ -11146,6 +11351,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
+        </is>
+      </c>
       <c r="Z141" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
@@ -11203,6 +11413,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
+        </is>
+      </c>
       <c r="Z142" t="inlineStr">
         <is>
           <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
@@ -11260,6 +11475,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
+        </is>
+      </c>
       <c r="Z143" t="inlineStr">
         <is>
           <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
@@ -11317,6 +11537,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
+        </is>
+      </c>
       <c r="Z144" t="inlineStr">
         <is>
           <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
@@ -11374,6 +11599,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
+        </is>
+      </c>
       <c r="Z145" t="inlineStr">
         <is>
           <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
@@ -11431,6 +11661,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
+        </is>
+      </c>
       <c r="Z146" t="inlineStr">
         <is>
           <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
@@ -11503,6 +11738,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
+        </is>
+      </c>
       <c r="Z147" t="inlineStr">
         <is>
           <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
@@ -11560,6 +11800,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
+        </is>
+      </c>
       <c r="Z148" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
@@ -11617,6 +11862,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
+        </is>
+      </c>
       <c r="Z149" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
@@ -11674,6 +11924,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
+        </is>
+      </c>
       <c r="Z150" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
@@ -11731,6 +11986,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
+        </is>
+      </c>
       <c r="Z151" t="inlineStr">
         <is>
           <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
@@ -11788,6 +12048,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
+        </is>
+      </c>
       <c r="Z152" t="inlineStr">
         <is>
           <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
@@ -11845,6 +12110,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
+        </is>
+      </c>
       <c r="Z153" t="inlineStr">
         <is>
           <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
@@ -11902,6 +12172,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
+        </is>
+      </c>
       <c r="Z154" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
@@ -11959,6 +12234,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
+        </is>
+      </c>
       <c r="Z155" t="inlineStr">
         <is>
           <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
@@ -12016,6 +12296,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
+        </is>
+      </c>
       <c r="Z156" t="inlineStr">
         <is>
           <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
@@ -12073,6 +12358,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
+        </is>
+      </c>
       <c r="Z157" t="inlineStr">
         <is>
           <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
@@ -12130,6 +12420,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
+        </is>
+      </c>
       <c r="Z158" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
@@ -12187,6 +12482,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
+        </is>
+      </c>
       <c r="Z159" t="inlineStr">
         <is>
           <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
@@ -12244,6 +12544,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
+        </is>
+      </c>
       <c r="Z160" t="inlineStr">
         <is>
           <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
@@ -12306,6 +12611,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
+        </is>
+      </c>
       <c r="Z161" t="inlineStr">
         <is>
           <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
@@ -12368,6 +12678,11 @@
           <t>If grabbed from the side or back then Cannonball will be the 1st part of the Multi Throw.</t>
         </is>
       </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
+        </is>
+      </c>
       <c r="Z162" t="inlineStr">
         <is>
           <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
@@ -12425,6 +12740,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
+        </is>
+      </c>
       <c r="Z163" t="inlineStr">
         <is>
           <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
@@ -12477,6 +12797,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
+        </is>
+      </c>
       <c r="Z164" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
@@ -12534,6 +12859,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
+        </is>
+      </c>
       <c r="Z165" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
@@ -12591,6 +12921,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
+        </is>
+      </c>
       <c r="Z166" t="inlineStr">
         <is>
           <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
@@ -12648,6 +12983,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>58f13036-58ee-4611-a14d-d783777422a0</t>
+        </is>
+      </c>
       <c r="Z167" t="inlineStr">
         <is>
           <t>58f13036-58ee-4611-a14d-d783777422a0</t>
@@ -12705,6 +13045,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
+        </is>
+      </c>
       <c r="Z168" t="inlineStr">
         <is>
           <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
@@ -12762,6 +13107,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
+        </is>
+      </c>
       <c r="Z169" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
@@ -12819,6 +13169,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
+        </is>
+      </c>
       <c r="Z170" t="inlineStr">
         <is>
           <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
@@ -12874,6 +13229,11 @@
       <c r="U171" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>cd229188-1f00-4e2c-beb7-0ecdab35b8dc</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
@@ -13078,6 +13438,11 @@
           <t>hhmmhLLLmM</t>
         </is>
       </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
+        </is>
+      </c>
       <c r="Z175" t="inlineStr">
         <is>
           <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
@@ -13125,6 +13490,11 @@
           <t>hhmmhLLLmh</t>
         </is>
       </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
+        </is>
+      </c>
       <c r="Z176" t="inlineStr">
         <is>
           <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
@@ -13172,6 +13542,11 @@
           <t>hhmmhmLLmM</t>
         </is>
       </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>d76e55af-5e37-469f-b459-858d5c452608</t>
+        </is>
+      </c>
       <c r="Z177" t="inlineStr">
         <is>
           <t>d76e55af-5e37-469f-b459-858d5c452608</t>
@@ -13219,6 +13594,11 @@
           <t>hhmmhmLLmh</t>
         </is>
       </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
+        </is>
+      </c>
       <c r="Z178" t="inlineStr">
         <is>
           <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
@@ -13266,6 +13646,11 @@
           <t>hhmmhmLLlthrow</t>
         </is>
       </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
+        </is>
+      </c>
       <c r="Z179" t="inlineStr">
         <is>
           <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
@@ -13313,6 +13698,11 @@
           <t>hmmhLLLmM</t>
         </is>
       </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
+        </is>
+      </c>
       <c r="Z180" t="inlineStr">
         <is>
           <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
@@ -13360,6 +13750,11 @@
           <t>hmmhLLLmh</t>
         </is>
       </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
+        </is>
+      </c>
       <c r="Z181" t="inlineStr">
         <is>
           <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
@@ -13407,6 +13802,11 @@
           <t>hmmhmLLmM</t>
         </is>
       </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
+        </is>
+      </c>
       <c r="Z182" t="inlineStr">
         <is>
           <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
@@ -13454,6 +13854,11 @@
           <t>hmmhmLLmh</t>
         </is>
       </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
+        </is>
+      </c>
       <c r="Z183" t="inlineStr">
         <is>
           <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
@@ -13499,6 +13904,11 @@
       <c r="S184" t="inlineStr">
         <is>
           <t>hmmhmLLlthrow</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>9aa5afc6-6646-4750-b84c-b3114de16321</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
